--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -37,8 +37,8 @@
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.00x"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,17 +149,18 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,7 +808,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26.6% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>28.8% -&gt; 17.2% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -869,7 +870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>Currency. EGP million unless stated. Spot EGP 130.00 (2026-09-03 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
@@ -1003,23 +1004,23 @@
       <c r="D5" s="24" t="n">
         <v>35961.076614</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -1084,7 +1085,7 @@
       <c r="C9" s="24" t="n">
         <v>38180.002322</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1095,13 +1096,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>151448.654828</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="32" t="n">
         <v>249527.138687</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="32" t="n">
         <v>311099.090775</v>
       </c>
       <c r="E10" s="13" t="n"/>
@@ -1164,32 +1165,32 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>35724.466132</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="32" t="n">
         <v>55274.913356</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="32" t="n">
         <v>66870.86655000001</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
@@ -1225,23 +1226,23 @@
       <c r="D16" s="24" t="n">
         <v>55852.53459999998</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="31">
         <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -1252,33 +1253,33 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>16214.447271</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <v>20902.939485</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
@@ -1289,35 +1290,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="37">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="37">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="37">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="37">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="37">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="37">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="37">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1328,15 +1329,15 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D10-(D11+D12+D13+D14+D15)</f>
         <v/>
       </c>
@@ -1478,7 +1479,7 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1493,7 +1494,7 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1508,7 +1509,7 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1523,12 +1524,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1560,12 +1561,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1630,12 +1631,12 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
@@ -1666,33 +1667,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -2051,17 +2052,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2132,12 +2133,12 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2555,111 +2556,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>64.02326653453551</v>
+        <v>54.89390300698878</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>66.87332082657952</v>
+        <v>56.76608049282878</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>70.27596109226505</v>
+        <v>58.9328825766538</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>74.4401253255354</v>
+        <v>61.49018601091854</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>79.69527743111146</v>
+        <v>64.58052940682644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>57.37629801344737</v>
+        <v>49.59394363429544</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>59.44490839625706</v>
+        <v>50.95326657112403</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>61.85495881829012</v>
+        <v>52.49104063008191</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>64.7211007280429</v>
+        <v>54.25965459765457</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>68.21578663977438</v>
+        <v>56.33422840926579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>51.7708075360223</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>53.27390215434404</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>54.98535884474298</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>56.96810019655753</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>49.7075887045515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46.98207982326851</v>
+        <v>41.11553668357441</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.06820632030645</v>
+        <v>41.8093978775642</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>49.27676996088003</v>
+        <v>42.55648627630665</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>50.64136360909256</v>
+        <v>43.36987034045674</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>52.20910626312477</v>
+        <v>44.26727799429032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>42.84560782729903</v>
+        <v>37.67472174247933</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>43.61959366674767</v>
+        <v>38.15151148948571</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>44.45954899997528</v>
+        <v>38.648345329237</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>45.3820571183214</v>
+        <v>39.16977223986016</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>46.40976788449724</v>
+        <v>39.72183036633324</v>
       </c>
     </row>
     <row r="12">
@@ -2673,138 +2674,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.9%</t>
+          <t>terminal 15.2%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>84.65984646706161</v>
+        <v>68.64247049591957</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>82.13279721284205</v>
+        <v>66.57546829677946</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>79.69527743111146</v>
+        <v>64.58052940682644</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.34332590623208</v>
+        <v>62.65451643723234</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.07319276143608</v>
+        <v>60.79445670792633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.9%</t>
+          <t>terminal 16.2%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>72.52574844266042</v>
+        <v>59.93237666911776</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>70.3319852695824</v>
+        <v>58.10144964510826</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>68.21578663977438</v>
+        <v>56.33422840926579</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>66.17372628576796</v>
+        <v>54.62794387184755</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>64.20256050533408</v>
+        <v>52.9799721331991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.9%</t>
+          <t>terminal 17.2%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>63.11573867848826</v>
+        <v>52.93321441251824</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>61.18033295945634</v>
+        <v>51.2919036374145</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>57.51138889928905</v>
+        <v>48.17779610598239</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>55.77198707016157</v>
+        <v>46.70018186414503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.9%</t>
+          <t>terminal 18.2%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>55.60688154053267</v>
+        <v>47.18722756407969</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>53.87754330288151</v>
+        <v>45.70150653374164</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>52.20910626312477</v>
+        <v>44.26727799429032</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>50.59888878852414</v>
+        <v>42.88231076920474</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>49.04435177713601</v>
+        <v>41.54449037834811</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.9%</t>
+          <t>terminal 19.2%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>49.47730377942706</v>
+        <v>42.38652255248041</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>47.91609946481731</v>
+        <v>41.03072689368742</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>46.40976788449724</v>
+        <v>39.72183036633324</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>44.95589663617206</v>
+        <v>38.45780396819539</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>43.55220138111397</v>
+        <v>37.23672469018629</v>
       </c>
     </row>
     <row r="20">
@@ -2835,23 +2836,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
+          <t>Beta  (0.60 / 0.80 / 1.23 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.05706087886328</v>
+        <v>94.46647146810956</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.37265613726478</v>
+        <v>75.25828072607085</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>49.70341773987482</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>51.92216787250401</v>
+        <v>53.21252849781632</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>45.39154463312268</v>
+        <v>46.50262521769896</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2865,19 +2866,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>53.41908966035297</v>
+        <v>42.07500523515485</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>59.60834905916349</v>
+        <v>46.38227967442072</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>64.76606522483894</v>
+        <v>49.97167504047564</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>69.92378139051441</v>
+        <v>53.56107040653055</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2891,19 +2892,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>31.52261532145548</v>
+        <v>23.17689166022818</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>43.50239572403932</v>
+        <v>33.3438275209025</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>67.46195652920696</v>
+        <v>53.67769924225113</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>79.4417369317908</v>
+        <v>63.84463510292543</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2917,19 +2918,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>52.3875464272179</v>
+        <v>41.3571261619439</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>53.9348612769205</v>
+        <v>42.43394477176034</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>57.02949097632575</v>
+        <v>44.58758199139326</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>58.57680582602841</v>
+        <v>45.66440060120974</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2943,19 +2944,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>62.73597456572764</v>
+        <v>50.27171997464177</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>58.98400985584599</v>
+        <v>46.77467346098749</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>51.48008043608273</v>
+        <v>39.7805804336789</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>47.72811572620108</v>
+        <v>36.28353392002459</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2969,19 +2970,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>48.93607870871411</v>
+        <v>40.98127111072365</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>55.75099900441143</v>
+        <v>46.71205527626227</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>66.23549176702268</v>
+        <v>55.52864630016783</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>69.38083959580605</v>
+        <v>58.17362360733951</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2995,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>51.7708075360223</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>53.27390215434404</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>54.98535884474298</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>56.96810019655753</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3472,35 +3473,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3511,36 +3512,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="37">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3787,12 +3788,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3809,12 +3810,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3831,12 +3832,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3853,12 +3854,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3882,7 +3883,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3893,7 +3894,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="35">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3904,7 +3905,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="35">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3915,7 +3916,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3926,7 +3927,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -4014,14 +4015,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19.89441449632232</v>
+        <v>16.18162005664932</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>104.9620537972264</v>
+        <v>83.79876343050132</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4230,7 +4231,7 @@
       </c>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="18" t="n">
-        <v>105.2</v>
+        <v>130</v>
       </c>
       <c r="D16" s="13" t="n"/>
       <c r="E16" s="13" t="n"/>
@@ -4427,7 +4428,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19.89441449632232</v>
+        <v>16.18162005664932</v>
       </c>
     </row>
     <row r="7">
@@ -4442,7 +4443,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>104.9620537972264</v>
+        <v>83.79876343050132</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4531,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>26.6% → 15.9%</t>
+          <t>28.8% → 17.2%</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4542,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
+        <f>(1-Assumptions!$C$65)*(Assumptions!$C$62+Assumptions!$C$33*Assumptions!$C$63)+Assumptions!$C$65*Assumptions!$C$64*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
@@ -4552,7 +4553,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>69.57809227740921</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="19">
@@ -4612,13 +4613,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>148.4077409306208</v>
+        <v>153.052652198775</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>108.8662301594048</v>
+        <v>112.2887963569921</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>187.9492517018369</v>
+        <v>193.8165080405579</v>
       </c>
     </row>
     <row r="24">
@@ -4633,13 +4634,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>72.81006662300985</v>
+        <v>65.48394099946414</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>36.13831647623267</v>
+        <v>34.12367903228015</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>65.71584535779077</v>
+        <v>59.75270243066323</v>
       </c>
     </row>
     <row r="25">
@@ -4654,13 +4655,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>54.45131359842825</v>
+        <v>45.28950840983638</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>46.88400987822836</v>
+        <v>42.22747080432825</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>69.57809227740921</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="26">
@@ -4688,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4775,7 +4776,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>105.2</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -5151,7 +5152,7 @@
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>1.009</v>
+        <v>1.224906574047969</v>
       </c>
     </row>
     <row r="34">
@@ -5353,17 +5354,17 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
+          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Currency-of-discounting alternative</t>
+          <t>Terminal construction — the sanctioned one, never g x IC</t>
         </is>
       </c>
       <c r="B55" s="13" t="n"/>
@@ -5377,94 +5378,148 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>US dollar risk-free rate</t>
+          <t>Terminal inflation (house Egyptian macro path)</t>
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>0.043</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Hard-currency-leg equity risk premium</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>0.075</v>
+          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="n">
+        <v>17.2627</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>US dollar cost of debt</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n">
-        <v>0.065</v>
+          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="n">
+        <v>110489.8413121987</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Debt weight, USD leg</t>
+          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Terminal growth of the USD leg</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>0.035</v>
-      </c>
+        <v>0.1219271916645494</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="13" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>US dollar risk-free rate</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>0.043</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="n">
-        <v>6.5</v>
+          <t>Hard-currency-leg equity risk premium</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C64" s="27" t="n">
-        <v>9</v>
+          <t>US dollar cost of debt</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n"/>
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="13" t="n"/>
+      <c r="H68" s="13" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C71" s="21" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -5479,7 +5534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5553,11 +5608,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5598,7 +5653,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5613,8 +5668,8 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="30">
-        <f>-C10*$C$15</f>
+      <c r="C11" s="31">
+        <f>-C10*$C$17</f>
         <v/>
       </c>
       <c r="D11" s="16">
@@ -5623,40 +5678,66 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Equity attributable to shareholders</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="31">
-        <f>C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Less the employees' statutory share of profit</t>
+        </is>
+      </c>
+      <c r="C12" s="29">
+        <f>-(C10+C11)*$C$18</f>
+        <v/>
+      </c>
+      <c r="D12" s="30">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Terminal value as a share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C14" s="17">
-        <f>DCF!C28</f>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Equity attributable to ordinary shareholders</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="32">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="33">
+        <f>C13/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>Terminal value as a share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>DCF!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Minority share of group profit</t>
         </is>
       </c>
-      <c r="C15" s="9">
+      <c r="C17" s="9">
         <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Employees' statutory share of profit — an appropriation disclosed only in the earnings-per-share note, below profit attributable to owners</t>
+        </is>
+      </c>
+      <c r="C18" s="17">
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
@@ -5856,7 +5937,7 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -5865,23 +5946,23 @@
         <v/>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="34">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="34">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="34">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -5990,23 +6071,23 @@
           <t>Group segment profit</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>SUM(F11:F13)</f>
         <v/>
       </c>
@@ -6076,23 +6157,23 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <f>B11-Assumptions!$B$22*E5</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>C11-Assumptions!$C$22*F5</f>
         <v/>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <f>D11-Assumptions!$D$22*G5</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <f>E11-Assumptions!$E$22*H5</f>
         <v/>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f>F11-Assumptions!$F$22*I5</f>
         <v/>
       </c>
@@ -6103,23 +6184,23 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B12-Assumptions!$B$22*E6</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C12-Assumptions!$C$22*F6</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D12-Assumptions!$D$22*G6</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>E12-Assumptions!$E$22*H6</f>
         <v/>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>F12-Assumptions!$F$22*I6</f>
         <v/>
       </c>
@@ -6130,23 +6211,23 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <f>B13-Assumptions!$B$22*E7</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>C13-Assumptions!$C$22*F7</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>D13-Assumptions!$D$22*G7</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>E13-Assumptions!$E$22*H7</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>F13-Assumptions!$F$22*I7</f>
         <v/>
       </c>
@@ -6157,23 +6238,23 @@
           <t>Group EBIT</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
@@ -6184,23 +6265,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>Assumptions!$C$27*E8</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>Assumptions!$C$27*F8</f>
         <v/>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>Assumptions!$C$27*G8</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>Assumptions!$C$27*H8</f>
         <v/>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
@@ -6211,23 +6292,23 @@
           <t>Group EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="34">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="34">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="34">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -6327,8 +6408,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="34">
-        <f>Assumptions!$C$63</f>
+      <c r="C6" s="35">
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -6338,7 +6419,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6349,7 +6430,7 @@
           <t>Discount factor back to the valuation date (year-2)</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6371,7 +6452,7 @@
           <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C7*C8+C9</f>
         <v/>
       </c>
@@ -6383,8 +6464,8 @@
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
-      <c r="C11" s="32">
-        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+      <c r="C11" s="33">
+        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6395,11 +6476,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6409,7 +6490,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6420,7 +6501,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6431,7 +6512,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6442,7 +6523,7 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6487,7 +6568,7 @@
           <t>Normalised EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6498,7 +6579,7 @@
           <t>Normalised EBIT (EGP mn)</t>
         </is>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6531,8 +6612,8 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="30">
-        <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
+      <c r="C25" s="31">
+        <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)</f>
         <v/>
       </c>
     </row>
@@ -6553,8 +6634,8 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="36">
-        <f>Assumptions!$C$64</f>
+      <c r="C27" s="37">
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -6565,7 +6646,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6613,7 +6694,7 @@
         </is>
       </c>
       <c r="C32" s="9">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -6645,7 +6726,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
@@ -6657,7 +6738,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n"/>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6667,11 +6748,11 @@
         </is>
       </c>
       <c r="E36" s="16">
-        <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$71-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$71+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6686,7 +6767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6835,23 +6916,23 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6862,23 +6943,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -6889,23 +6970,23 @@
           <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -6916,23 +6997,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>-F8</f>
         <v/>
       </c>
@@ -6943,23 +7024,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
@@ -6970,23 +7051,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -6997,23 +7078,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7024,23 +7105,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="38">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7051,23 +7132,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="39">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="39">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -7078,23 +7159,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -7109,40 +7190,40 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Terminal-year NOPAT grown one year (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="30">
-        <f>F10*(1+C23)</f>
+          <t>Terminal-year NOPAT — the LAST EXPLICIT year (FY2030), NOT grown (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C20" s="31">
+        <f>F10</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C21" s="17">
-        <f>F10*(1+C23)/'Summary Financials'!I13</f>
+          <t>Add back FY2030 book depreciation and amortisation (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="31">
+        <f>-F8</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Required reinvestment rate (g / return on capital)</t>
-        </is>
-      </c>
-      <c r="C22" s="9">
-        <f>C23/C21</f>
+          <t>Terminal free cash flow to the firm — C20 + C21 less the capital charge on rows 65-67</t>
+        </is>
+      </c>
+      <c r="C22" s="31">
+        <f>C20+C21+C65+C66+C67</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal growth (nominal, derived from zero real growth and terminal inflation)</t>
         </is>
       </c>
       <c r="C23" s="17">
@@ -7164,11 +7245,11 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C25" s="30">
-        <f>C20*(1-C22)/(C24-C23)</f>
+          <t>Terminal value — C22 grown one year and capitalised at (C24 − C23) (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="31">
+        <f>C22*(1+C23)/(C24-C23)</f>
         <v/>
       </c>
     </row>
@@ -7178,7 +7259,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7189,7 +7270,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7211,7 +7292,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7219,11 +7300,11 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders (EGP mn)</t>
+          <t>Equity attributable to ordinary shareholders (EGP mn)</t>
         </is>
       </c>
       <c r="C30" s="19">
-        <f>'SOTP Bridge'!C12</f>
+        <f>'SOTP Bridge'!C13</f>
         <v/>
       </c>
     </row>
@@ -7234,7 +7315,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n"/>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7275,7 +7356,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="38">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7286,7 +7367,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="40">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
@@ -7308,7 +7389,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="38">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7330,7 +7411,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="38">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7363,7 +7444,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="38">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7374,7 +7455,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="38">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7386,7 +7467,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n"/>
-      <c r="C46" s="40">
+      <c r="C46" s="41">
         <f>C45*C39+C44*C41</f>
         <v/>
       </c>
@@ -7420,7 +7501,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="38">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7442,7 +7523,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="37">
+      <c r="C51" s="38">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7465,7 +7546,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n"/>
-      <c r="C53" s="40">
+      <c r="C53" s="41">
         <f>(1-C52)*C49+C52*C51</f>
         <v/>
       </c>
@@ -7536,23 +7617,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="38">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="37">
+      <c r="C57" s="38">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="37">
+      <c r="D57" s="38">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="37">
+      <c r="E57" s="38">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="37">
+      <c r="F57" s="38">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7577,7 +7658,7 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="39">
         <f>(1+C39)^(Assumptions!$C$53/365)</f>
         <v/>
       </c>
@@ -7585,11 +7666,11 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
+          <t>Fair value per share at the 3-Sep-2026 anchor (EGP)</t>
         </is>
       </c>
       <c r="B62" s="13" t="n"/>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <f>C31*C61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -7600,6 +7681,57 @@
         <is>
           <t>The bridge on row 31 is dated 31-Dec-2025 (the audited balance-sheet date it subtracts net debt at). Row 62 rolls it to the anchor at the cost of equity, net of the EGP 1.85 FY2025 dividend paid in the window. Every lens on every sheet is rolled the same way.</t>
         </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>THE TERMINAL'S CAPITAL CHARGE — MAINTENANCE AT CURRENT COST, NEVER g x IC</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Less maintenance capital at current replacement cost — FY2030 book depreciation escalated over half the DISCLOSED useful life</t>
+        </is>
+      </c>
+      <c r="C65" s="19">
+        <f>F8*(1+Assumptions!$C$56)^(Assumptions!$C$57/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Less capital for real growth — zero, because the stated real growth is zero</t>
+        </is>
+      </c>
+      <c r="C66" s="31">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Less inflation on the terminal working-capital base</t>
+        </is>
+      </c>
+      <c r="C67" s="19">
+        <f>-Assumptions!$C$58*Assumptions!$C$56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital (disclosure — it drives nothing here; the retired construction that used it charged g x IC every year for ever, which reads as replacing the whole asset base every 1/g years and is a fact about the inflation rate rather than about the asset)</t>
+        </is>
+      </c>
+      <c r="C68" s="9">
+        <f>F10*(1+C23)/'Summary Financials'!I13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -7702,32 +7834,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>152186.247545</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <v>231981.835577</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>281049.081719</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7774,32 +7906,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>20035.105205</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <v>31601.46495</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>28363.203246</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -7885,35 +8017,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="32">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -7933,23 +8065,23 @@
       <c r="D11" s="24" t="n">
         <v>-2145.438755</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
@@ -7969,23 +8101,23 @@
       <c r="D12" s="24" t="n">
         <v>1568.902975</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>D12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>E12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>F12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>G12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
@@ -7996,35 +8128,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8044,23 +8176,23 @@
       <c r="D14" s="24" t="n">
         <v>-5591.139782</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8080,23 +8212,23 @@
       <c r="D15" s="24" t="n">
         <v>19186.550057</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8116,24 +8248,24 @@
       <c r="D16" s="24" t="n">
         <v>-1856.305067000001</v>
       </c>
-      <c r="E16" s="30">
-        <f>-E15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>-F15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="G16" s="30">
-        <f>-G15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>-H15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="I16" s="30">
-        <f>-I15*'SOTP Bridge'!$C$15</f>
+      <c r="E16" s="31">
+        <f>-E15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="F16" s="31">
+        <f>-F15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="G16" s="31">
+        <f>-G15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="H16" s="31">
+        <f>-H15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="I16" s="31">
+        <f>-I15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
     </row>
@@ -8143,32 +8275,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>10115.701777</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <v>17461.358714</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="32" t="n">
         <v>17330.24499</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>I15+I16</f>
         <v/>
       </c>
